--- a/data/raw/survey_responses.xlsx
+++ b/data/raw/survey_responses.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1922" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2212" uniqueCount="439">
   <si>
     <t>Carimbo de data/hora</t>
   </si>
@@ -1787,6 +1787,129 @@
   </si>
   <si>
     <t>thaysferreiraua@gmail.com</t>
+  </si>
+  <si>
+    <t>Paraná</t>
+  </si>
+  <si>
+    <t>Origem</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Escala</t>
+  </si>
+  <si>
+    <t>Distribuição</t>
+  </si>
+  <si>
+    <t>Uso</t>
+  </si>
+  <si>
+    <t>Eu sempre participo. Inicialmente, as necessidades dos clientes são identificadas. Posteriormente são priorizadas e descritas. As tarefas são divididas em sprints e estimadas nas reuniões de planejamento. Os devs recebem as tarefas de acordo com o capacity e senioridade/especialidade. Utilizamos scrum e kanbam. As tasks são entregues de forma continua em pequenos pacotes de atualizações.</t>
+  </si>
+  <si>
+    <t>O mais fundamental é que os dados precisam ser não-ambíguos pois a tomada de decisão precisa ser assertiva. Executar uma ação crítica como por exemplo bloquear o cartão de um cliente 5 estrelas é péssimo. Os dados precisam estar sempre disponíveis, consistentes e atuais. Eu vejo uma grande relação entre consistência e atualidade. Por exemplo, um cliente pode ser tornar inadimplente a qualquer momento. Dados atuais são essenciais principalmente para startups.</t>
+  </si>
+  <si>
+    <t>Quanto mais consistentes os dados, melhor a classificação.</t>
+  </si>
+  <si>
+    <t>Depende muito do projeto. Projetos que envolvem saúde ou dinheiro são mais críticos em relação à alguns pontos. Agora alguns tipos de classificação podem ter outras prioridades.</t>
+  </si>
+  <si>
+    <t>Dados incompletos ou ausentes, Falta de padronização nos formatos de dados, Dados desatualizados ou não confiáveis, Erros introduzidos durante a coleta e processamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Especialista </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normalização </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribuição </t>
+  </si>
+  <si>
+    <t>Normalmente não participo muito na etapa de engenharia de requisitos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precisão é importante pois um dado impreciso causaria erros de aprendizado e predição nos modelos que aprenderiam com esses dados.  Completude é importante pois na vida real o modelo utilizado poderia simplesmente não ser capaz de prever uma observação corretamente pois o dado de treinamento utilizado para este modelo falta exemplos suficientes daquele tipo de dado. </t>
+  </si>
+  <si>
+    <t>Dependendo da situação, infelizmente talvez não tenhamos opções nem de equilibrar. Mas completude, precisão, e credibilidade devem ser prioritários.</t>
+  </si>
+  <si>
+    <t>Linguagem estruturada (texto), Relatórios Periódicos</t>
+  </si>
+  <si>
+    <t>Fonte confiavel</t>
+  </si>
+  <si>
+    <t>Padrao</t>
+  </si>
+  <si>
+    <t>Explicabilidade</t>
+  </si>
+  <si>
+    <t>Relaçao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Em alguna projetos sim, nesse caso procuro fontes de dados confiaveis que tem relacao ao problema a ser resolvido. As vezes os dados que temos nao tem relacao real com o.problema, ou nao se sabe de fato qual é o problema </t>
+  </si>
+  <si>
+    <t>Acredito que todas as características são importantes,  e precisam serem.levadas para o uso industrial. Em algum nível.</t>
+  </si>
+  <si>
+    <t>Depende da criticisade do modelo, onde ele vai ser implementado e as politicas da equipe de trabalho. Muitas vezes conciliar as caracteristicas tem.uma relacao maior com o trabalho da equipe do projeto e os prazos de entrega. Ainda temos dificuldade de que  vonsiderem o estudo previo dos dados como entregavel de uma sprint pois acham que modelos sao como pasteis, feitos rapidos, com qualquer dados e tecnologia. E  resolve o mundo</t>
+  </si>
+  <si>
+    <t>coleta</t>
+  </si>
+  <si>
+    <t>fonte</t>
+  </si>
+  <si>
+    <t>banco de dados</t>
+  </si>
+  <si>
+    <t>anotaçao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mediçao </t>
+  </si>
+  <si>
+    <t>Não tenho experiência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faço muito uso de dados desequências de DNA, tais caracteristicas estão relacionadas com a plataforma que se utiliza, sendo assim tento manter sempre plataformas atualizadas </t>
+  </si>
+  <si>
+    <t>Reuniões de Alinhamento, Relatórios Periódicos</t>
+  </si>
+  <si>
+    <t>Erros introduzidos durante a coleta e processamento, Falta de ferramentas adequadas para validação da qualidade dos dados</t>
+  </si>
+  <si>
+    <t>Fora, Dublin/Irlanda</t>
+  </si>
+  <si>
+    <t>Sem viés</t>
+  </si>
+  <si>
+    <t>É um processo oneroso, mas se bem feito é extremamente útil no projeto. O que acaba sendo chato são as atualizações necessárias no documento para que ele se mantenha relevante.</t>
+  </si>
+  <si>
+    <t>Os itens marcados como importantes não sinalizam que os modelos serão menos performáticos. Ainda é possível extrair boas métricas tendo uma base de dados que possui os itens demarcados como muito importantes.</t>
+  </si>
+  <si>
+    <t>É procurar entregar um MVP com os dados que temos. Em seguida, deixar nas mãos do negócio para decisões de onde o projeto irá.</t>
+  </si>
+  <si>
+    <t>Avaliação inicial durante a coleta e preparação de dados, Monitoramento contínuo durante todo o ciclo de vida do modelo, Não existe uma estratégia formal para assegurar a qualidade dos dados durante o desenvolvimento.</t>
+  </si>
+  <si>
+    <t>Linguagem estruturada (texto), Documentação Centralizada (Sistemas como Confluence, Google Docs ou Notion)</t>
   </si>
 </sst>
 </file>
@@ -1888,8 +2011,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:BK33" displayName="Form_Responses1" name="Form_Responses1" id="1" totalsRowShown="0">
-  <autoFilter ref="A1:BK33"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:BK38" displayName="Form_Responses1" name="Form_Responses1" id="1" totalsRowShown="0">
+  <autoFilter ref="A1:BK38"/>
   <tableColumns count="63">
     <tableColumn name="Carimbo de data/hora" id="1"/>
     <tableColumn name="O Termo de Consentimento Livre e Esclarecido (TCLE) visa assegurar seus direitos como participante e está disponível nesse link. Por favor, leia com atenção e calma, buscando entender completamente a proposta da pesquisa. Não haverá nenhum tipo de penalização ou prejuízo se você não quiser participar ou retirar sua autorização em qualquer momento." id="2"/>
@@ -2247,7 +2370,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:BK33"/>
+  <dimension ref="A1:BK38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="7" width="21.290714285714284" customWidth="1" bestFit="1"/>
@@ -8432,6 +8555,931 @@
       </c>
       <c r="BK33" s="6"/>
     </row>
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="22.5">
+      <c r="A34" s="1">
+        <v>46140.64270833333</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I34" s="5">
+        <v>4</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="P34" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q34" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="R34" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="S34" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="T34" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="U34" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="V34" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="W34" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="X34" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="Y34" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="Z34" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA34" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB34" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AC34" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD34" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AE34" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AF34" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG34" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH34" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI34" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AJ34" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AK34" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL34" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AM34" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="AN34" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AO34" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AP34" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ34" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AR34" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AS34" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AT34" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AU34" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AV34" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW34" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AX34" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AY34" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AZ34" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="BA34" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="BB34" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="BC34" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="BD34" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="BE34" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="BF34" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="BG34" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="BH34" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="BI34" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="BJ34" s="6"/>
+      <c r="BK34" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="22.5">
+      <c r="A35" s="1">
+        <v>46141.448541666665</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I35" s="5">
+        <v>6</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="U35" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="V35" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="W35" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="X35" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y35" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="Z35" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA35" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB35" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC35" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AD35" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE35" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF35" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG35" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH35" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI35" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="AJ35" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AK35" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL35" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AM35" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="AN35" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO35" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP35" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AQ35" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR35" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AS35" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AT35" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AU35" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AV35" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AW35" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AX35" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AY35" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AZ35" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BA35" s="6"/>
+      <c r="BB35" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="BC35" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="BD35" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="BE35" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="BF35" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="BG35" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="BH35" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="BI35" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="BJ35" s="6"/>
+      <c r="BK35" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="22.5">
+      <c r="A36" s="1">
+        <v>46141.534907407404</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="I36" s="5">
+        <v>25</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="P36" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q36" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="R36" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="S36" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="T36" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="U36" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="V36" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="W36" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="X36" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="Y36" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="Z36" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA36" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB36" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AC36" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AD36" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AE36" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF36" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG36" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH36" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI36" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AJ36" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AK36" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AL36" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AM36" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="AN36" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AO36" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AP36" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AQ36" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR36" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AS36" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AT36" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AU36" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AV36" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW36" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AX36" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AY36" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AZ36" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="BA36" s="6"/>
+      <c r="BB36" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="BC36" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="BD36" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="BE36" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="BF36" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="BG36" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="BH36" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="BI36" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="BJ36" s="6"/>
+      <c r="BK36" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="22.5">
+      <c r="A37" s="1">
+        <v>46141.70155092593</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="I37" s="5">
+        <v>8</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O37" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P37" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q37" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R37" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="S37" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="T37" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="U37" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="V37" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="W37" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="X37" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="Y37" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="Z37" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA37" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB37" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AC37" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AD37" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AE37" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF37" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG37" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH37" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AI37" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AJ37" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK37" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AL37" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AM37" s="6"/>
+      <c r="AN37" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO37" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AP37" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AQ37" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AR37" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AS37" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AT37" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AU37" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AV37" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AW37" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AX37" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AY37" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AZ37" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="BA37" s="6"/>
+      <c r="BB37" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="BC37" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="BD37" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="BE37" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="BF37" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="BG37" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="BH37" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="BI37" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="BJ37" s="6"/>
+      <c r="BK37" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="22.5">
+      <c r="A38" s="1">
+        <v>46141.71136574074</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I38" s="5">
+        <v>3</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P38" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q38" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="R38" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="S38" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="T38" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="U38" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="V38" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="W38" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="X38" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="Y38" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="Z38" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA38" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB38" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AC38" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AD38" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AE38" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AF38" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG38" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH38" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI38" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AJ38" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AK38" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL38" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AM38" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="AN38" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AO38" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AP38" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ38" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR38" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AS38" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AT38" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AU38" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AV38" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW38" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AX38" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AY38" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AZ38" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="BA38" s="6"/>
+      <c r="BB38" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="BC38" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="BD38" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="BE38" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="BF38" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="BG38" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="BH38" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="BI38" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="BJ38" s="6"/>
+      <c r="BK38" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
